--- a/assets/template/year2.xlsx
+++ b/assets/template/year2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\laragon\www\qc\assets\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A7F055F-560D-4CBF-9528-EE5D31CB8EF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54E62869-DADD-4AF0-8F77-493EF1863347}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,102 +30,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
-    <r>
-      <t xml:space="preserve">Stt
-</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>S. No</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Tên sản phẩm
-</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Product name</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Số lô
-</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Batch No.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Mã số sản phẩm
-</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Product code</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Mã số đề cương
-</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Protocol No.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">KẾ HOẠCH NGHIÊN CỨU ĐỘ ỔN ĐỊNH HÀNG NĂM - NĂM [….]
-</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>ANNUAL PLAN FOR STABILITY STUDY - YEAR [….]</t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">Viên nang mềm Diệp Hạ Châu </t>
   </si>
   <si>
@@ -134,20 +38,104 @@
   <si>
     <t>241001</t>
   </si>
+  <si>
+    <r>
+      <t xml:space="preserve">KẾ HOẠCH NGHIÊN CỨU ĐỘ ỔN ĐỊNH HÀNG NĂM - NĂM [….]
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>ANNUAL PLAN FOR STABILITY STUDY - YEAR [….]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Stt
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>S. No</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Tên sản phẩm
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Product name</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Số lô
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Batch No.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Mã số sản phẩm
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Product code</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Mã số đề cương
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Protocol No.</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="2"/>
@@ -160,13 +148,6 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <i/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
@@ -186,17 +167,16 @@
       <family val="1"/>
     </font>
     <font>
-      <i/>
-      <sz val="9"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="9"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
-      <family val="2"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -282,51 +262,51 @@
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -658,290 +638,290 @@
   <dimension ref="A1:W12"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15.75" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.77734375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="21.44140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="8.77734375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="8.5546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.109375" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.77734375" style="1"/>
+    <col min="1" max="1" width="5.77734375" style="16" customWidth="1"/>
+    <col min="2" max="2" width="21.44140625" style="16" customWidth="1"/>
+    <col min="3" max="3" width="8.77734375" style="16" customWidth="1"/>
+    <col min="4" max="4" width="8.5546875" style="16" customWidth="1"/>
+    <col min="5" max="5" width="11.109375" style="16" customWidth="1"/>
+    <col min="6" max="16384" width="8.77734375" style="16"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="11"/>
-      <c r="B1" s="11"/>
-      <c r="C1" s="12" t="s">
+    <row r="1" spans="1:23" s="4" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="8"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
+      <c r="P1" s="6"/>
+      <c r="Q1" s="6"/>
+      <c r="R1" s="6"/>
+      <c r="S1" s="6"/>
+      <c r="T1" s="6"/>
+      <c r="U1" s="6"/>
+      <c r="V1" s="6"/>
+      <c r="W1" s="6"/>
+    </row>
+    <row r="2" spans="1:23" s="4" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6"/>
+      <c r="S2" s="6"/>
+      <c r="T2" s="6"/>
+      <c r="U2" s="6"/>
+      <c r="V2" s="6"/>
+      <c r="W2" s="6"/>
+    </row>
+    <row r="3" spans="1:23" s="4" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
-      <c r="N1" s="9"/>
-      <c r="O1" s="9"/>
-      <c r="P1" s="9"/>
-      <c r="Q1" s="9"/>
-      <c r="R1" s="9"/>
-      <c r="S1" s="9"/>
-      <c r="T1" s="9"/>
-      <c r="U1" s="9"/>
-      <c r="V1" s="9"/>
-      <c r="W1" s="9"/>
-    </row>
-    <row r="2" spans="1:23" s="7" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6"/>
-      <c r="B2" s="6"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
-      <c r="N2" s="9"/>
-      <c r="O2" s="9"/>
-      <c r="P2" s="9"/>
-      <c r="Q2" s="9"/>
-      <c r="R2" s="9"/>
-      <c r="S2" s="9"/>
-      <c r="T2" s="9"/>
-      <c r="U2" s="9"/>
-      <c r="V2" s="9"/>
-      <c r="W2" s="9"/>
-    </row>
-    <row r="3" spans="1:23" s="7" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
+      <c r="C3" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6"/>
+      <c r="U3" s="6"/>
+      <c r="V3" s="6"/>
+      <c r="W3" s="6"/>
+    </row>
+    <row r="4" spans="1:23" s="5" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="12"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="7"/>
+      <c r="O4" s="7"/>
+      <c r="P4" s="7"/>
+      <c r="Q4" s="7"/>
+      <c r="R4" s="7"/>
+      <c r="S4" s="7"/>
+      <c r="T4" s="7"/>
+      <c r="U4" s="7"/>
+      <c r="V4" s="7"/>
+      <c r="W4" s="7"/>
+    </row>
+    <row r="5" spans="1:23" s="5" customFormat="1" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="13"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="7"/>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7"/>
+      <c r="O5" s="7"/>
+      <c r="P5" s="7"/>
+      <c r="Q5" s="7"/>
+      <c r="R5" s="7"/>
+      <c r="S5" s="7"/>
+      <c r="T5" s="7"/>
+      <c r="U5" s="7"/>
+      <c r="V5" s="7"/>
+      <c r="W5" s="7"/>
+    </row>
+    <row r="6" spans="1:23" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A6" s="3"/>
+      <c r="B6" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="C6" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
-      <c r="N3" s="9"/>
-      <c r="O3" s="9"/>
-      <c r="P3" s="9"/>
-      <c r="Q3" s="9"/>
-      <c r="R3" s="9"/>
-      <c r="S3" s="9"/>
-      <c r="T3" s="9"/>
-      <c r="U3" s="9"/>
-      <c r="V3" s="9"/>
-      <c r="W3" s="9"/>
-    </row>
-    <row r="4" spans="1:23" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="15"/>
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
-      <c r="L4" s="10"/>
-      <c r="M4" s="10"/>
-      <c r="N4" s="10"/>
-      <c r="O4" s="10"/>
-      <c r="P4" s="10"/>
-      <c r="Q4" s="10"/>
-      <c r="R4" s="10"/>
-      <c r="S4" s="10"/>
-      <c r="T4" s="10"/>
-      <c r="U4" s="10"/>
-      <c r="V4" s="10"/>
-      <c r="W4" s="10"/>
-    </row>
-    <row r="5" spans="1:23" s="8" customFormat="1" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="16"/>
-      <c r="B5" s="16"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="10"/>
-      <c r="L5" s="10"/>
-      <c r="M5" s="10"/>
-      <c r="N5" s="10"/>
-      <c r="O5" s="10"/>
-      <c r="P5" s="10"/>
-      <c r="Q5" s="10"/>
-      <c r="R5" s="10"/>
-      <c r="S5" s="10"/>
-      <c r="T5" s="10"/>
-      <c r="U5" s="10"/>
-      <c r="V5" s="10"/>
-      <c r="W5" s="10"/>
-    </row>
-    <row r="6" spans="1:23" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A6" s="6"/>
-      <c r="B6" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="5">
+      <c r="E6" s="15">
         <v>2101010011</v>
       </c>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9"/>
-      <c r="K6" s="9"/>
-      <c r="L6" s="9"/>
-      <c r="M6" s="9"/>
-      <c r="N6" s="9"/>
-      <c r="O6" s="9"/>
-      <c r="P6" s="9"/>
-      <c r="Q6" s="9"/>
-      <c r="R6" s="9"/>
-      <c r="S6" s="9"/>
-      <c r="T6" s="9"/>
-      <c r="U6" s="9"/>
-      <c r="V6" s="9"/>
-      <c r="W6" s="9"/>
-    </row>
-    <row r="7" spans="1:23" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A7" s="6"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="9"/>
-      <c r="L7" s="9"/>
-      <c r="M7" s="9"/>
-      <c r="N7" s="9"/>
-      <c r="O7" s="9"/>
-      <c r="P7" s="9"/>
-      <c r="Q7" s="9"/>
-      <c r="R7" s="9"/>
-      <c r="S7" s="9"/>
-      <c r="T7" s="9"/>
-      <c r="U7" s="9"/>
-      <c r="V7" s="9"/>
-      <c r="W7" s="9"/>
-    </row>
-    <row r="8" spans="1:23" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="9"/>
-      <c r="K8" s="9"/>
-      <c r="L8" s="9"/>
-      <c r="M8" s="9"/>
-      <c r="N8" s="9"/>
-      <c r="O8" s="9"/>
-      <c r="P8" s="9"/>
-      <c r="Q8" s="9"/>
-      <c r="R8" s="9"/>
-      <c r="S8" s="9"/>
-      <c r="T8" s="9"/>
-      <c r="U8" s="9"/>
-      <c r="V8" s="9"/>
-      <c r="W8" s="9"/>
-    </row>
-    <row r="9" spans="1:23" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
-      <c r="K9" s="9"/>
-      <c r="L9" s="9"/>
-      <c r="M9" s="9"/>
-      <c r="N9" s="9"/>
-      <c r="O9" s="9"/>
-      <c r="P9" s="9"/>
-      <c r="Q9" s="9"/>
-      <c r="R9" s="9"/>
-      <c r="S9" s="9"/>
-      <c r="T9" s="9"/>
-      <c r="U9" s="9"/>
-      <c r="V9" s="9"/>
-      <c r="W9" s="9"/>
-    </row>
-    <row r="10" spans="1:23" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
-      <c r="K10" s="9"/>
-      <c r="L10" s="9"/>
-      <c r="M10" s="9"/>
-      <c r="N10" s="9"/>
-      <c r="O10" s="9"/>
-      <c r="P10" s="9"/>
-      <c r="Q10" s="9"/>
-      <c r="R10" s="9"/>
-      <c r="S10" s="9"/>
-      <c r="T10" s="9"/>
-      <c r="U10" s="9"/>
-      <c r="V10" s="9"/>
-      <c r="W10" s="9"/>
-    </row>
-    <row r="11" spans="1:23" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
-      <c r="K11" s="9"/>
-      <c r="L11" s="9"/>
-      <c r="M11" s="9"/>
-      <c r="N11" s="9"/>
-      <c r="O11" s="9"/>
-      <c r="P11" s="9"/>
-      <c r="Q11" s="9"/>
-      <c r="R11" s="9"/>
-      <c r="S11" s="9"/>
-      <c r="T11" s="9"/>
-      <c r="U11" s="9"/>
-      <c r="V11" s="9"/>
-      <c r="W11" s="9"/>
-    </row>
-    <row r="12" spans="1:23" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="6"/>
+      <c r="P6" s="6"/>
+      <c r="Q6" s="6"/>
+      <c r="R6" s="6"/>
+      <c r="S6" s="6"/>
+      <c r="T6" s="6"/>
+      <c r="U6" s="6"/>
+      <c r="V6" s="6"/>
+      <c r="W6" s="6"/>
+    </row>
+    <row r="7" spans="1:23" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A7" s="3"/>
+      <c r="B7" s="14"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="6"/>
+      <c r="O7" s="6"/>
+      <c r="P7" s="6"/>
+      <c r="Q7" s="6"/>
+      <c r="R7" s="6"/>
+      <c r="S7" s="6"/>
+      <c r="T7" s="6"/>
+      <c r="U7" s="6"/>
+      <c r="V7" s="6"/>
+      <c r="W7" s="6"/>
+    </row>
+    <row r="8" spans="1:23" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
+      <c r="N8" s="6"/>
+      <c r="O8" s="6"/>
+      <c r="P8" s="6"/>
+      <c r="Q8" s="6"/>
+      <c r="R8" s="6"/>
+      <c r="S8" s="6"/>
+      <c r="T8" s="6"/>
+      <c r="U8" s="6"/>
+      <c r="V8" s="6"/>
+      <c r="W8" s="6"/>
+    </row>
+    <row r="9" spans="1:23" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="6"/>
+      <c r="O9" s="6"/>
+      <c r="P9" s="6"/>
+      <c r="Q9" s="6"/>
+      <c r="R9" s="6"/>
+      <c r="S9" s="6"/>
+      <c r="T9" s="6"/>
+      <c r="U9" s="6"/>
+      <c r="V9" s="6"/>
+      <c r="W9" s="6"/>
+    </row>
+    <row r="10" spans="1:23" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="6"/>
+      <c r="M10" s="6"/>
+      <c r="N10" s="6"/>
+      <c r="O10" s="6"/>
+      <c r="P10" s="6"/>
+      <c r="Q10" s="6"/>
+      <c r="R10" s="6"/>
+      <c r="S10" s="6"/>
+      <c r="T10" s="6"/>
+      <c r="U10" s="6"/>
+      <c r="V10" s="6"/>
+      <c r="W10" s="6"/>
+    </row>
+    <row r="11" spans="1:23" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6"/>
+      <c r="L11" s="6"/>
+      <c r="M11" s="6"/>
+      <c r="N11" s="6"/>
+      <c r="O11" s="6"/>
+      <c r="P11" s="6"/>
+      <c r="Q11" s="6"/>
+      <c r="R11" s="6"/>
+      <c r="S11" s="6"/>
+      <c r="T11" s="6"/>
+      <c r="U11" s="6"/>
+      <c r="V11" s="6"/>
+      <c r="W11" s="6"/>
+    </row>
+    <row r="12" spans="1:23" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="A1:B1"/>
@@ -957,7 +937,7 @@
   <headerFooter>
     <oddHeader xml:space="preserve">&amp;C&amp;12
 </oddHeader>
-    <oddFooter>&amp;L&amp;12Mã số phụ lục / &amp;"Times New Roman,Italic"Appendix No.&amp;"Times New Roman,Regular" 0002020_A02_02&amp;C&amp;12Ngày hiệu lực / &amp;"Times New Roman,Italic"Appendix effective&amp;"Times New Roman,Regular" 18/01/2024&amp;R&amp;12Trang / Page &amp;P/&amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;12Mã số phụ lục / Appendix No. 0002020_A02_02&amp;C&amp;12Ngày hiệu lực / Appendix effective 18/01/2024&amp;R&amp;12Trang / Page &amp;P/&amp;N</oddFooter>
   </headerFooter>
   <drawing r:id="rId2"/>
 </worksheet>

--- a/assets/template/year2.xlsx
+++ b/assets/template/year2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\laragon\www\qc\assets\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54E62869-DADD-4AF0-8F77-493EF1863347}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82A4BC23-CC04-4256-B5B9-C6361D22DEFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t xml:space="preserve">Viên nang mềm Diệp Hạ Châu </t>
   </si>
@@ -39,101 +39,43 @@
     <t>241001</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">KẾ HOẠCH NGHIÊN CỨU ĐỘ ỔN ĐỊNH HÀNG NĂM - NĂM [….]
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>ANNUAL PLAN FOR STABILITY STUDY - YEAR [….]</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Stt
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>S. No</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Tên sản phẩm
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Product name</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Số lô
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Batch No.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Mã số sản phẩm
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Product code</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Mã số đề cương
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Protocol No.</t>
-    </r>
+    <t>Khu vực
+Area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KẾ HOẠCH NGHIÊN CỨU ĐỘ ỔN ĐỊNH HÀNG NĂM
+ANNUAL PLAN FOR STABILITY STUDY </t>
+  </si>
+  <si>
+    <t>Năm
+Year</t>
+  </si>
+  <si>
+    <t>Stt
+S. No</t>
+  </si>
+  <si>
+    <t>Tên sản phẩm
+Product name</t>
+  </si>
+  <si>
+    <t>Số lô
+Batch No.</t>
+  </si>
+  <si>
+    <t>Mã số sản phẩm
+Product code</t>
+  </si>
+  <si>
+    <t>Mã số đề cương
+Protocol No.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
       <color theme="1"/>
@@ -147,21 +89,7 @@
       <family val="1"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
       <sz val="10"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
@@ -178,6 +106,25 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -187,7 +134,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -214,15 +161,6 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -256,57 +194,132 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -330,41 +343,54 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>161925</xdr:colOff>
+      <xdr:colOff>200025</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:rowOff>219075</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1205342</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>481965</xdr:rowOff>
+      <xdr:colOff>1285875</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>137632</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3">
+        <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AAAA058A-5886-4B79-845A-5E6A6C8E1689}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvPicPr/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
-      <xdr:spPr>
+      <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="657225" y="47625"/>
-          <a:ext cx="1043417" cy="434340"/>
+          <a:off x="695325" y="219075"/>
+          <a:ext cx="1085850" cy="451957"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -635,302 +661,327 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W12"/>
+  <dimension ref="A1:AG12"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15.75" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.77734375" style="16" customWidth="1"/>
-    <col min="2" max="2" width="21.44140625" style="16" customWidth="1"/>
-    <col min="3" max="3" width="8.77734375" style="16" customWidth="1"/>
-    <col min="4" max="4" width="8.5546875" style="16" customWidth="1"/>
-    <col min="5" max="5" width="11.109375" style="16" customWidth="1"/>
-    <col min="6" max="16384" width="8.77734375" style="16"/>
+    <col min="1" max="1" width="5.77734375" style="9" customWidth="1"/>
+    <col min="2" max="2" width="21.44140625" style="9" customWidth="1"/>
+    <col min="3" max="3" width="8.77734375" style="9" customWidth="1"/>
+    <col min="4" max="4" width="8.5546875" style="9" customWidth="1"/>
+    <col min="5" max="5" width="11.109375" style="9" customWidth="1"/>
+    <col min="6" max="16384" width="8.77734375" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" s="4" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="8"/>
-      <c r="B1" s="8"/>
-      <c r="C1" s="9" t="s">
+    <row r="1" spans="1:33" s="16" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="11"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="13"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="14"/>
+      <c r="Q1" s="15"/>
+      <c r="R1" s="15"/>
+      <c r="S1" s="15"/>
+      <c r="T1" s="15"/>
+      <c r="U1" s="15"/>
+      <c r="V1" s="15"/>
+      <c r="W1" s="15"/>
+      <c r="X1" s="15"/>
+      <c r="Y1" s="15"/>
+      <c r="Z1" s="15"/>
+      <c r="AA1" s="15"/>
+      <c r="AB1" s="15"/>
+      <c r="AC1" s="15"/>
+      <c r="AD1" s="15"/>
+      <c r="AE1" s="15"/>
+      <c r="AF1" s="15"/>
+      <c r="AG1" s="15"/>
+    </row>
+    <row r="2" spans="1:33" s="16" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="17"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="6"/>
-      <c r="U1" s="6"/>
-      <c r="V1" s="6"/>
-      <c r="W1" s="6"/>
-    </row>
-    <row r="2" spans="1:23" s="4" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6"/>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="6"/>
-      <c r="R2" s="6"/>
-      <c r="S2" s="6"/>
-      <c r="T2" s="6"/>
-      <c r="U2" s="6"/>
-      <c r="V2" s="6"/>
-      <c r="W2" s="6"/>
-    </row>
-    <row r="3" spans="1:23" s="4" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="11" t="s">
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="13"/>
+      <c r="M2" s="13"/>
+      <c r="N2" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="O2" s="19"/>
+      <c r="P2" s="15"/>
+      <c r="Q2" s="15"/>
+      <c r="R2" s="15"/>
+      <c r="S2" s="15"/>
+      <c r="T2" s="15"/>
+      <c r="U2" s="15"/>
+      <c r="V2" s="15"/>
+      <c r="W2" s="15"/>
+      <c r="X2" s="15"/>
+      <c r="Y2" s="15"/>
+      <c r="Z2" s="15"/>
+      <c r="AA2" s="15"/>
+      <c r="AB2" s="15"/>
+      <c r="AC2" s="15"/>
+      <c r="AD2" s="15"/>
+      <c r="AE2" s="15"/>
+      <c r="AF2" s="15"/>
+      <c r="AG2" s="15"/>
+    </row>
+    <row r="3" spans="1:33" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="B3" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="C3" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6"/>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="6"/>
-      <c r="S3" s="6"/>
-      <c r="T3" s="6"/>
-      <c r="U3" s="6"/>
-      <c r="V3" s="6"/>
-      <c r="W3" s="6"/>
-    </row>
-    <row r="4" spans="1:23" s="5" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="12"/>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
-      <c r="M4" s="7"/>
-      <c r="N4" s="7"/>
-      <c r="O4" s="7"/>
-      <c r="P4" s="7"/>
-      <c r="Q4" s="7"/>
-      <c r="R4" s="7"/>
-      <c r="S4" s="7"/>
-      <c r="T4" s="7"/>
-      <c r="U4" s="7"/>
-      <c r="V4" s="7"/>
-      <c r="W4" s="7"/>
-    </row>
-    <row r="5" spans="1:23" s="5" customFormat="1" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="13"/>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="7"/>
-      <c r="M5" s="7"/>
-      <c r="N5" s="7"/>
-      <c r="O5" s="7"/>
-      <c r="P5" s="7"/>
-      <c r="Q5" s="7"/>
-      <c r="R5" s="7"/>
-      <c r="S5" s="7"/>
-      <c r="T5" s="7"/>
-      <c r="U5" s="7"/>
-      <c r="V5" s="7"/>
-      <c r="W5" s="7"/>
-    </row>
-    <row r="6" spans="1:23" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A6" s="3"/>
-      <c r="B6" s="14" t="s">
+      <c r="D3" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="5"/>
+      <c r="R3" s="5"/>
+      <c r="S3" s="5"/>
+      <c r="T3" s="5"/>
+      <c r="U3" s="5"/>
+      <c r="V3" s="5"/>
+      <c r="W3" s="5"/>
+    </row>
+    <row r="4" spans="1:33" s="4" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="21"/>
+      <c r="B4" s="21"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="6"/>
+      <c r="T4" s="6"/>
+      <c r="U4" s="6"/>
+      <c r="V4" s="6"/>
+      <c r="W4" s="6"/>
+    </row>
+    <row r="5" spans="1:33" s="4" customFormat="1" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="22"/>
+      <c r="B5" s="22"/>
+      <c r="C5" s="22"/>
+      <c r="D5" s="22"/>
+      <c r="E5" s="22"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="6"/>
+      <c r="P5" s="6"/>
+      <c r="Q5" s="6"/>
+      <c r="R5" s="6"/>
+      <c r="S5" s="6"/>
+      <c r="T5" s="6"/>
+      <c r="U5" s="6"/>
+      <c r="V5" s="6"/>
+      <c r="W5" s="6"/>
+    </row>
+    <row r="6" spans="1:33" s="3" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A6" s="2"/>
+      <c r="B6" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="E6" s="15">
+      <c r="E6" s="8">
         <v>2101010011</v>
       </c>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6"/>
-      <c r="K6" s="6"/>
-      <c r="L6" s="6"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="6"/>
-      <c r="Q6" s="6"/>
-      <c r="R6" s="6"/>
-      <c r="S6" s="6"/>
-      <c r="T6" s="6"/>
-      <c r="U6" s="6"/>
-      <c r="V6" s="6"/>
-      <c r="W6" s="6"/>
-    </row>
-    <row r="7" spans="1:23" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A7" s="3"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="6"/>
-      <c r="O7" s="6"/>
-      <c r="P7" s="6"/>
-      <c r="Q7" s="6"/>
-      <c r="R7" s="6"/>
-      <c r="S7" s="6"/>
-      <c r="T7" s="6"/>
-      <c r="U7" s="6"/>
-      <c r="V7" s="6"/>
-      <c r="W7" s="6"/>
-    </row>
-    <row r="8" spans="1:23" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="6"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="6"/>
-      <c r="O8" s="6"/>
-      <c r="P8" s="6"/>
-      <c r="Q8" s="6"/>
-      <c r="R8" s="6"/>
-      <c r="S8" s="6"/>
-      <c r="T8" s="6"/>
-      <c r="U8" s="6"/>
-      <c r="V8" s="6"/>
-      <c r="W8" s="6"/>
-    </row>
-    <row r="9" spans="1:23" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
-      <c r="K9" s="6"/>
-      <c r="L9" s="6"/>
-      <c r="M9" s="6"/>
-      <c r="N9" s="6"/>
-      <c r="O9" s="6"/>
-      <c r="P9" s="6"/>
-      <c r="Q9" s="6"/>
-      <c r="R9" s="6"/>
-      <c r="S9" s="6"/>
-      <c r="T9" s="6"/>
-      <c r="U9" s="6"/>
-      <c r="V9" s="6"/>
-      <c r="W9" s="6"/>
-    </row>
-    <row r="10" spans="1:23" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
-      <c r="J10" s="6"/>
-      <c r="K10" s="6"/>
-      <c r="L10" s="6"/>
-      <c r="M10" s="6"/>
-      <c r="N10" s="6"/>
-      <c r="O10" s="6"/>
-      <c r="P10" s="6"/>
-      <c r="Q10" s="6"/>
-      <c r="R10" s="6"/>
-      <c r="S10" s="6"/>
-      <c r="T10" s="6"/>
-      <c r="U10" s="6"/>
-      <c r="V10" s="6"/>
-      <c r="W10" s="6"/>
-    </row>
-    <row r="11" spans="1:23" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6"/>
-      <c r="K11" s="6"/>
-      <c r="L11" s="6"/>
-      <c r="M11" s="6"/>
-      <c r="N11" s="6"/>
-      <c r="O11" s="6"/>
-      <c r="P11" s="6"/>
-      <c r="Q11" s="6"/>
-      <c r="R11" s="6"/>
-      <c r="S11" s="6"/>
-      <c r="T11" s="6"/>
-      <c r="U11" s="6"/>
-      <c r="V11" s="6"/>
-      <c r="W11" s="6"/>
-    </row>
-    <row r="12" spans="1:23" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="5"/>
+      <c r="Q6" s="5"/>
+      <c r="R6" s="5"/>
+      <c r="S6" s="5"/>
+      <c r="T6" s="5"/>
+      <c r="U6" s="5"/>
+      <c r="V6" s="5"/>
+      <c r="W6" s="5"/>
+    </row>
+    <row r="7" spans="1:33" s="3" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A7" s="2"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5"/>
+      <c r="L7" s="5"/>
+      <c r="M7" s="5"/>
+      <c r="N7" s="5"/>
+      <c r="O7" s="5"/>
+      <c r="P7" s="5"/>
+      <c r="Q7" s="5"/>
+      <c r="R7" s="5"/>
+      <c r="S7" s="5"/>
+      <c r="T7" s="5"/>
+      <c r="U7" s="5"/>
+      <c r="V7" s="5"/>
+      <c r="W7" s="5"/>
+    </row>
+    <row r="8" spans="1:33" s="3" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="5"/>
+      <c r="P8" s="5"/>
+      <c r="Q8" s="5"/>
+      <c r="R8" s="5"/>
+      <c r="S8" s="5"/>
+      <c r="T8" s="5"/>
+      <c r="U8" s="5"/>
+      <c r="V8" s="5"/>
+      <c r="W8" s="5"/>
+    </row>
+    <row r="9" spans="1:33" s="3" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="5"/>
+      <c r="M9" s="5"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="5"/>
+      <c r="Q9" s="5"/>
+      <c r="R9" s="5"/>
+      <c r="S9" s="5"/>
+      <c r="T9" s="5"/>
+      <c r="U9" s="5"/>
+      <c r="V9" s="5"/>
+      <c r="W9" s="5"/>
+    </row>
+    <row r="10" spans="1:33" s="3" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="5"/>
+      <c r="M10" s="5"/>
+      <c r="N10" s="5"/>
+      <c r="O10" s="5"/>
+      <c r="P10" s="5"/>
+      <c r="Q10" s="5"/>
+      <c r="R10" s="5"/>
+      <c r="S10" s="5"/>
+      <c r="T10" s="5"/>
+      <c r="U10" s="5"/>
+      <c r="V10" s="5"/>
+      <c r="W10" s="5"/>
+    </row>
+    <row r="11" spans="1:33" s="3" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="5"/>
+      <c r="M11" s="5"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="5"/>
+      <c r="P11" s="5"/>
+      <c r="Q11" s="5"/>
+      <c r="R11" s="5"/>
+      <c r="S11" s="5"/>
+      <c r="T11" s="5"/>
+      <c r="U11" s="5"/>
+      <c r="V11" s="5"/>
+      <c r="W11" s="5"/>
+    </row>
+    <row r="12" spans="1:33" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:F1"/>
+  <mergeCells count="8">
     <mergeCell ref="A3:A5"/>
     <mergeCell ref="B3:B5"/>
     <mergeCell ref="C3:C5"/>
     <mergeCell ref="D3:D5"/>
     <mergeCell ref="E3:E5"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:O1"/>
+    <mergeCell ref="D2:M2"/>
   </mergeCells>
   <pageMargins left="0.51181102362204722" right="0.23622047244094491" top="0.51181102362204722" bottom="0.51181102362204722" header="0.23622047244094491" footer="0.23622047244094491"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>

--- a/assets/template/year2.xlsx
+++ b/assets/template/year2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\laragon\www\qc\assets\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82A4BC23-CC04-4256-B5B9-C6361D22DEFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02E1488A-1E05-471A-9E97-1C560386DE3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -255,7 +255,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -285,40 +285,46 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -672,108 +678,108 @@
     <col min="6" max="16384" width="8.77734375" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" s="16" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="11"/>
-      <c r="B1" s="12"/>
-      <c r="C1" s="13" t="s">
+    <row r="1" spans="1:33" s="14" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="18"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="14"/>
-      <c r="Q1" s="15"/>
-      <c r="R1" s="15"/>
-      <c r="S1" s="15"/>
-      <c r="T1" s="15"/>
-      <c r="U1" s="15"/>
-      <c r="V1" s="15"/>
-      <c r="W1" s="15"/>
-      <c r="X1" s="15"/>
-      <c r="Y1" s="15"/>
-      <c r="Z1" s="15"/>
-      <c r="AA1" s="15"/>
-      <c r="AB1" s="15"/>
-      <c r="AC1" s="15"/>
-      <c r="AD1" s="15"/>
-      <c r="AE1" s="15"/>
-      <c r="AF1" s="15"/>
-      <c r="AG1" s="15"/>
-    </row>
-    <row r="2" spans="1:33" s="16" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="17"/>
-      <c r="B2" s="18"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
+      <c r="M1" s="22"/>
+      <c r="N1" s="22"/>
+      <c r="O1" s="22"/>
+      <c r="P1" s="12"/>
+      <c r="Q1" s="13"/>
+      <c r="R1" s="13"/>
+      <c r="S1" s="13"/>
+      <c r="T1" s="13"/>
+      <c r="U1" s="13"/>
+      <c r="V1" s="13"/>
+      <c r="W1" s="13"/>
+      <c r="X1" s="13"/>
+      <c r="Y1" s="13"/>
+      <c r="Z1" s="13"/>
+      <c r="AA1" s="13"/>
+      <c r="AB1" s="13"/>
+      <c r="AC1" s="13"/>
+      <c r="AD1" s="13"/>
+      <c r="AE1" s="13"/>
+      <c r="AF1" s="13"/>
+      <c r="AG1" s="13"/>
+    </row>
+    <row r="2" spans="1:33" s="14" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="20"/>
+      <c r="B2" s="21"/>
       <c r="C2" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
-      <c r="M2" s="13"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="22"/>
+      <c r="L2" s="22"/>
+      <c r="M2" s="22"/>
       <c r="N2" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="O2" s="19"/>
-      <c r="P2" s="15"/>
-      <c r="Q2" s="15"/>
-      <c r="R2" s="15"/>
-      <c r="S2" s="15"/>
-      <c r="T2" s="15"/>
-      <c r="U2" s="15"/>
-      <c r="V2" s="15"/>
-      <c r="W2" s="15"/>
-      <c r="X2" s="15"/>
-      <c r="Y2" s="15"/>
-      <c r="Z2" s="15"/>
-      <c r="AA2" s="15"/>
-      <c r="AB2" s="15"/>
-      <c r="AC2" s="15"/>
-      <c r="AD2" s="15"/>
-      <c r="AE2" s="15"/>
-      <c r="AF2" s="15"/>
-      <c r="AG2" s="15"/>
+      <c r="O2" s="11"/>
+      <c r="P2" s="13"/>
+      <c r="Q2" s="13"/>
+      <c r="R2" s="13"/>
+      <c r="S2" s="13"/>
+      <c r="T2" s="13"/>
+      <c r="U2" s="13"/>
+      <c r="V2" s="13"/>
+      <c r="W2" s="13"/>
+      <c r="X2" s="13"/>
+      <c r="Y2" s="13"/>
+      <c r="Z2" s="13"/>
+      <c r="AA2" s="13"/>
+      <c r="AB2" s="13"/>
+      <c r="AC2" s="13"/>
+      <c r="AD2" s="13"/>
+      <c r="AE2" s="13"/>
+      <c r="AF2" s="13"/>
+      <c r="AG2" s="13"/>
     </row>
     <row r="3" spans="1:33" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="D3" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="E3" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
+      <c r="I3" s="24"/>
+      <c r="J3" s="24"/>
+      <c r="K3" s="24"/>
+      <c r="L3" s="24"/>
+      <c r="M3" s="24"/>
+      <c r="N3" s="24"/>
+      <c r="O3" s="24"/>
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
@@ -784,21 +790,11 @@
       <c r="W3" s="5"/>
     </row>
     <row r="4" spans="1:33" s="4" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="21"/>
-      <c r="B4" s="21"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="6"/>
-      <c r="O4" s="6"/>
+      <c r="A4" s="16"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
@@ -809,21 +805,11 @@
       <c r="W4" s="6"/>
     </row>
     <row r="5" spans="1:33" s="4" customFormat="1" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="22"/>
-      <c r="B5" s="22"/>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="6"/>
-      <c r="O5" s="6"/>
+      <c r="A5" s="17"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
@@ -847,16 +833,16 @@
       <c r="E6" s="8">
         <v>2101010011</v>
       </c>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="5"/>
-      <c r="O6" s="5"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="23"/>
+      <c r="H6" s="23"/>
+      <c r="I6" s="23"/>
+      <c r="J6" s="23"/>
+      <c r="K6" s="23"/>
+      <c r="L6" s="23"/>
+      <c r="M6" s="23"/>
+      <c r="N6" s="23"/>
+      <c r="O6" s="23"/>
       <c r="P6" s="5"/>
       <c r="Q6" s="5"/>
       <c r="R6" s="5"/>
@@ -872,16 +858,16 @@
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
       <c r="E7" s="8"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
-      <c r="M7" s="5"/>
-      <c r="N7" s="5"/>
-      <c r="O7" s="5"/>
+      <c r="F7" s="23"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="23"/>
+      <c r="I7" s="23"/>
+      <c r="J7" s="23"/>
+      <c r="K7" s="23"/>
+      <c r="L7" s="23"/>
+      <c r="M7" s="23"/>
+      <c r="N7" s="23"/>
+      <c r="O7" s="23"/>
       <c r="P7" s="5"/>
       <c r="Q7" s="5"/>
       <c r="R7" s="5"/>
@@ -892,16 +878,16 @@
       <c r="W7" s="5"/>
     </row>
     <row r="8" spans="1:33" s="3" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5"/>
-      <c r="M8" s="5"/>
-      <c r="N8" s="5"/>
-      <c r="O8" s="5"/>
+      <c r="F8" s="23"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="23"/>
+      <c r="I8" s="23"/>
+      <c r="J8" s="23"/>
+      <c r="K8" s="23"/>
+      <c r="L8" s="23"/>
+      <c r="M8" s="23"/>
+      <c r="N8" s="23"/>
+      <c r="O8" s="23"/>
       <c r="P8" s="5"/>
       <c r="Q8" s="5"/>
       <c r="R8" s="5"/>
@@ -912,16 +898,16 @@
       <c r="W8" s="5"/>
     </row>
     <row r="9" spans="1:33" s="3" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5"/>
-      <c r="M9" s="5"/>
-      <c r="N9" s="5"/>
-      <c r="O9" s="5"/>
+      <c r="F9" s="23"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="23"/>
+      <c r="I9" s="23"/>
+      <c r="J9" s="23"/>
+      <c r="K9" s="23"/>
+      <c r="L9" s="23"/>
+      <c r="M9" s="23"/>
+      <c r="N9" s="23"/>
+      <c r="O9" s="23"/>
       <c r="P9" s="5"/>
       <c r="Q9" s="5"/>
       <c r="R9" s="5"/>
@@ -932,16 +918,16 @@
       <c r="W9" s="5"/>
     </row>
     <row r="10" spans="1:33" s="3" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
-      <c r="L10" s="5"/>
-      <c r="M10" s="5"/>
-      <c r="N10" s="5"/>
-      <c r="O10" s="5"/>
+      <c r="F10" s="23"/>
+      <c r="G10" s="23"/>
+      <c r="H10" s="23"/>
+      <c r="I10" s="23"/>
+      <c r="J10" s="23"/>
+      <c r="K10" s="23"/>
+      <c r="L10" s="23"/>
+      <c r="M10" s="23"/>
+      <c r="N10" s="23"/>
+      <c r="O10" s="23"/>
       <c r="P10" s="5"/>
       <c r="Q10" s="5"/>
       <c r="R10" s="5"/>
@@ -952,16 +938,16 @@
       <c r="W10" s="5"/>
     </row>
     <row r="11" spans="1:33" s="3" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5"/>
-      <c r="L11" s="5"/>
-      <c r="M11" s="5"/>
-      <c r="N11" s="5"/>
-      <c r="O11" s="5"/>
+      <c r="F11" s="23"/>
+      <c r="G11" s="23"/>
+      <c r="H11" s="23"/>
+      <c r="I11" s="23"/>
+      <c r="J11" s="23"/>
+      <c r="K11" s="23"/>
+      <c r="L11" s="23"/>
+      <c r="M11" s="23"/>
+      <c r="N11" s="23"/>
+      <c r="O11" s="23"/>
       <c r="P11" s="5"/>
       <c r="Q11" s="5"/>
       <c r="R11" s="5"/>
@@ -974,14 +960,14 @@
     <row r="12" spans="1:33" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:O1"/>
+    <mergeCell ref="D2:M2"/>
     <mergeCell ref="A3:A5"/>
     <mergeCell ref="B3:B5"/>
     <mergeCell ref="C3:C5"/>
     <mergeCell ref="D3:D5"/>
     <mergeCell ref="E3:E5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:O1"/>
-    <mergeCell ref="D2:M2"/>
   </mergeCells>
   <pageMargins left="0.51181102362204722" right="0.23622047244094491" top="0.51181102362204722" bottom="0.51181102362204722" header="0.23622047244094491" footer="0.23622047244094491"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>

--- a/assets/template/year2.xlsx
+++ b/assets/template/year2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\laragon\www\qc\assets\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02E1488A-1E05-471A-9E97-1C560386DE3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F455CC89-4730-49CB-AF5A-900C905A2EF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -297,6 +297,27 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -304,27 +325,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -679,23 +679,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:33" s="14" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="18"/>
-      <c r="B1" s="19"/>
-      <c r="C1" s="22" t="s">
+      <c r="A1" s="17"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
-      <c r="K1" s="22"/>
-      <c r="L1" s="22"/>
-      <c r="M1" s="22"/>
-      <c r="N1" s="22"/>
-      <c r="O1" s="22"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="21"/>
+      <c r="O1" s="21"/>
       <c r="P1" s="12"/>
       <c r="Q1" s="13"/>
       <c r="R1" s="13"/>
@@ -716,21 +716,21 @@
       <c r="AG1" s="13"/>
     </row>
     <row r="2" spans="1:33" s="14" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="20"/>
-      <c r="B2" s="21"/>
+      <c r="A2" s="19"/>
+      <c r="B2" s="20"/>
       <c r="C2" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="22"/>
-      <c r="K2" s="22"/>
-      <c r="L2" s="22"/>
-      <c r="M2" s="22"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="21"/>
+      <c r="K2" s="21"/>
+      <c r="L2" s="21"/>
+      <c r="M2" s="21"/>
       <c r="N2" s="10" t="s">
         <v>5</v>
       </c>
@@ -755,31 +755,31 @@
       <c r="AG2" s="13"/>
     </row>
     <row r="3" spans="1:33" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="D3" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="E3" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24"/>
-      <c r="J3" s="24"/>
-      <c r="K3" s="24"/>
-      <c r="L3" s="24"/>
-      <c r="M3" s="24"/>
-      <c r="N3" s="24"/>
-      <c r="O3" s="24"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="16"/>
+      <c r="J3" s="16"/>
+      <c r="K3" s="16"/>
+      <c r="L3" s="16"/>
+      <c r="M3" s="16"/>
+      <c r="N3" s="16"/>
+      <c r="O3" s="16"/>
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
@@ -790,11 +790,11 @@
       <c r="W3" s="5"/>
     </row>
     <row r="4" spans="1:33" s="4" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="16"/>
-      <c r="B4" s="16"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
+      <c r="A4" s="23"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
@@ -805,11 +805,11 @@
       <c r="W4" s="6"/>
     </row>
     <row r="5" spans="1:33" s="4" customFormat="1" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="17"/>
-      <c r="B5" s="17"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
+      <c r="A5" s="24"/>
+      <c r="B5" s="24"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
@@ -833,16 +833,16 @@
       <c r="E6" s="8">
         <v>2101010011</v>
       </c>
-      <c r="F6" s="23"/>
-      <c r="G6" s="23"/>
-      <c r="H6" s="23"/>
-      <c r="I6" s="23"/>
-      <c r="J6" s="23"/>
-      <c r="K6" s="23"/>
-      <c r="L6" s="23"/>
-      <c r="M6" s="23"/>
-      <c r="N6" s="23"/>
-      <c r="O6" s="23"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="15"/>
+      <c r="L6" s="15"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="15"/>
+      <c r="O6" s="15"/>
       <c r="P6" s="5"/>
       <c r="Q6" s="5"/>
       <c r="R6" s="5"/>
@@ -858,16 +858,16 @@
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
       <c r="E7" s="8"/>
-      <c r="F7" s="23"/>
-      <c r="G7" s="23"/>
-      <c r="H7" s="23"/>
-      <c r="I7" s="23"/>
-      <c r="J7" s="23"/>
-      <c r="K7" s="23"/>
-      <c r="L7" s="23"/>
-      <c r="M7" s="23"/>
-      <c r="N7" s="23"/>
-      <c r="O7" s="23"/>
+      <c r="F7" s="15"/>
+      <c r="G7" s="15"/>
+      <c r="H7" s="15"/>
+      <c r="I7" s="15"/>
+      <c r="J7" s="15"/>
+      <c r="K7" s="15"/>
+      <c r="L7" s="15"/>
+      <c r="M7" s="15"/>
+      <c r="N7" s="15"/>
+      <c r="O7" s="15"/>
       <c r="P7" s="5"/>
       <c r="Q7" s="5"/>
       <c r="R7" s="5"/>
@@ -878,16 +878,16 @@
       <c r="W7" s="5"/>
     </row>
     <row r="8" spans="1:33" s="3" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="F8" s="23"/>
-      <c r="G8" s="23"/>
-      <c r="H8" s="23"/>
-      <c r="I8" s="23"/>
-      <c r="J8" s="23"/>
-      <c r="K8" s="23"/>
-      <c r="L8" s="23"/>
-      <c r="M8" s="23"/>
-      <c r="N8" s="23"/>
-      <c r="O8" s="23"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="15"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="15"/>
+      <c r="M8" s="15"/>
+      <c r="N8" s="15"/>
+      <c r="O8" s="15"/>
       <c r="P8" s="5"/>
       <c r="Q8" s="5"/>
       <c r="R8" s="5"/>
@@ -898,16 +898,16 @@
       <c r="W8" s="5"/>
     </row>
     <row r="9" spans="1:33" s="3" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="F9" s="23"/>
-      <c r="G9" s="23"/>
-      <c r="H9" s="23"/>
-      <c r="I9" s="23"/>
-      <c r="J9" s="23"/>
-      <c r="K9" s="23"/>
-      <c r="L9" s="23"/>
-      <c r="M9" s="23"/>
-      <c r="N9" s="23"/>
-      <c r="O9" s="23"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="15"/>
+      <c r="H9" s="15"/>
+      <c r="I9" s="15"/>
+      <c r="J9" s="15"/>
+      <c r="K9" s="15"/>
+      <c r="L9" s="15"/>
+      <c r="M9" s="15"/>
+      <c r="N9" s="15"/>
+      <c r="O9" s="15"/>
       <c r="P9" s="5"/>
       <c r="Q9" s="5"/>
       <c r="R9" s="5"/>
@@ -918,16 +918,16 @@
       <c r="W9" s="5"/>
     </row>
     <row r="10" spans="1:33" s="3" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="F10" s="23"/>
-      <c r="G10" s="23"/>
-      <c r="H10" s="23"/>
-      <c r="I10" s="23"/>
-      <c r="J10" s="23"/>
-      <c r="K10" s="23"/>
-      <c r="L10" s="23"/>
-      <c r="M10" s="23"/>
-      <c r="N10" s="23"/>
-      <c r="O10" s="23"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="15"/>
+      <c r="L10" s="15"/>
+      <c r="M10" s="15"/>
+      <c r="N10" s="15"/>
+      <c r="O10" s="15"/>
       <c r="P10" s="5"/>
       <c r="Q10" s="5"/>
       <c r="R10" s="5"/>
@@ -938,16 +938,16 @@
       <c r="W10" s="5"/>
     </row>
     <row r="11" spans="1:33" s="3" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="F11" s="23"/>
-      <c r="G11" s="23"/>
-      <c r="H11" s="23"/>
-      <c r="I11" s="23"/>
-      <c r="J11" s="23"/>
-      <c r="K11" s="23"/>
-      <c r="L11" s="23"/>
-      <c r="M11" s="23"/>
-      <c r="N11" s="23"/>
-      <c r="O11" s="23"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="15"/>
+      <c r="I11" s="15"/>
+      <c r="J11" s="15"/>
+      <c r="K11" s="15"/>
+      <c r="L11" s="15"/>
+      <c r="M11" s="15"/>
+      <c r="N11" s="15"/>
+      <c r="O11" s="15"/>
       <c r="P11" s="5"/>
       <c r="Q11" s="5"/>
       <c r="R11" s="5"/>
@@ -974,7 +974,7 @@
   <headerFooter>
     <oddHeader xml:space="preserve">&amp;C&amp;12
 </oddHeader>
-    <oddFooter>&amp;L&amp;12Mã số phụ lục / Appendix No. 0002020_A02_02&amp;C&amp;12Ngày hiệu lực / Appendix effective 18/01/2024&amp;R&amp;12Trang / Page &amp;P/&amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;12Mã số phụ lục / Appendix No. 0002020_A02_03&amp;C&amp;12Ngày hiệu lực / Appendix effective 28/05/2024&amp;R&amp;12Trang / Page &amp;P/&amp;N</oddFooter>
   </headerFooter>
   <drawing r:id="rId2"/>
 </worksheet>

--- a/assets/template/year2.xlsx
+++ b/assets/template/year2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\laragon\www\qc\assets\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F455CC89-4730-49CB-AF5A-900C905A2EF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{895F10BD-502D-47AF-A59A-27FD88BC43F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t xml:space="preserve">Viên nang mềm Diệp Hạ Châu </t>
   </si>
@@ -69,13 +69,21 @@
   <si>
     <t>Mã số đề cương
 Protocol No.</t>
+  </si>
+  <si>
+    <t>Người lập / Ngày
+Prepared by / Date</t>
+  </si>
+  <si>
+    <t>Người phê duyệt / Ngày
+Approved by / Date</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
       <color theme="1"/>
@@ -122,6 +130,17 @@
       <b/>
       <sz val="12"/>
       <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -255,7 +274,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -326,6 +345,18 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -667,7 +698,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AG12"/>
+  <dimension ref="A1:AG14"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15.75" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.77734375" style="9" customWidth="1"/>
@@ -958,8 +989,44 @@
       <c r="W11" s="5"/>
     </row>
     <row r="12" spans="1:33" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:33" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="25"/>
+      <c r="B13" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="27"/>
+      <c r="D13" s="27"/>
+      <c r="E13" s="27"/>
+      <c r="F13" s="27"/>
+      <c r="G13" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="H13" s="27"/>
+      <c r="I13" s="27"/>
+      <c r="J13" s="27"/>
+      <c r="K13" s="27"/>
+      <c r="P13" s="25"/>
+    </row>
+    <row r="14" spans="1:33" customFormat="1" ht="159" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="25"/>
+      <c r="B14" s="28"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="28"/>
+      <c r="G14" s="28"/>
+      <c r="H14" s="28"/>
+      <c r="I14" s="28"/>
+      <c r="J14" s="28"/>
+      <c r="K14" s="28"/>
+      <c r="P14" s="25"/>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="12">
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="G13:K13"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="G14:K14"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:O1"/>
     <mergeCell ref="D2:M2"/>

--- a/assets/template/year2.xlsx
+++ b/assets/template/year2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\laragon\www\qc\assets\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{895F10BD-502D-47AF-A59A-27FD88BC43F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33F54667-9E95-4529-9D51-A034EABEF287}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -274,13 +274,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -322,6 +319,18 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -345,18 +354,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -701,325 +698,329 @@
   <dimension ref="A1:AG14"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15.75" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.77734375" style="9" customWidth="1"/>
-    <col min="2" max="2" width="21.44140625" style="9" customWidth="1"/>
-    <col min="3" max="3" width="8.77734375" style="9" customWidth="1"/>
-    <col min="4" max="4" width="8.5546875" style="9" customWidth="1"/>
-    <col min="5" max="5" width="11.109375" style="9" customWidth="1"/>
-    <col min="6" max="16384" width="8.77734375" style="9"/>
+    <col min="1" max="1" width="5.77734375" style="8" customWidth="1"/>
+    <col min="2" max="2" width="21.44140625" style="8" customWidth="1"/>
+    <col min="3" max="3" width="8.77734375" style="8" customWidth="1"/>
+    <col min="4" max="4" width="8.5546875" style="8" customWidth="1"/>
+    <col min="5" max="5" width="11.109375" style="8" customWidth="1"/>
+    <col min="6" max="16384" width="8.77734375" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" s="14" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="17"/>
-      <c r="B1" s="18"/>
-      <c r="C1" s="21" t="s">
+    <row r="1" spans="1:33" s="13" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="20"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
-      <c r="M1" s="21"/>
-      <c r="N1" s="21"/>
-      <c r="O1" s="21"/>
-      <c r="P1" s="12"/>
-      <c r="Q1" s="13"/>
-      <c r="R1" s="13"/>
-      <c r="S1" s="13"/>
-      <c r="T1" s="13"/>
-      <c r="U1" s="13"/>
-      <c r="V1" s="13"/>
-      <c r="W1" s="13"/>
-      <c r="X1" s="13"/>
-      <c r="Y1" s="13"/>
-      <c r="Z1" s="13"/>
-      <c r="AA1" s="13"/>
-      <c r="AB1" s="13"/>
-      <c r="AC1" s="13"/>
-      <c r="AD1" s="13"/>
-      <c r="AE1" s="13"/>
-      <c r="AF1" s="13"/>
-      <c r="AG1" s="13"/>
-    </row>
-    <row r="2" spans="1:33" s="14" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="19"/>
-      <c r="B2" s="20"/>
-      <c r="C2" s="10" t="s">
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+      <c r="L1" s="24"/>
+      <c r="M1" s="24"/>
+      <c r="N1" s="24"/>
+      <c r="O1" s="24"/>
+      <c r="P1" s="11"/>
+      <c r="Q1" s="12"/>
+      <c r="R1" s="12"/>
+      <c r="S1" s="12"/>
+      <c r="T1" s="12"/>
+      <c r="U1" s="12"/>
+      <c r="V1" s="12"/>
+      <c r="W1" s="12"/>
+      <c r="X1" s="12"/>
+      <c r="Y1" s="12"/>
+      <c r="Z1" s="12"/>
+      <c r="AA1" s="12"/>
+      <c r="AB1" s="12"/>
+      <c r="AC1" s="12"/>
+      <c r="AD1" s="12"/>
+      <c r="AE1" s="12"/>
+      <c r="AF1" s="12"/>
+      <c r="AG1" s="12"/>
+    </row>
+    <row r="2" spans="1:33" s="13" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="22"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="21"/>
-      <c r="J2" s="21"/>
-      <c r="K2" s="21"/>
-      <c r="L2" s="21"/>
-      <c r="M2" s="21"/>
-      <c r="N2" s="10" t="s">
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="24"/>
+      <c r="L2" s="24"/>
+      <c r="M2" s="24"/>
+      <c r="N2" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="O2" s="11"/>
-      <c r="P2" s="13"/>
-      <c r="Q2" s="13"/>
-      <c r="R2" s="13"/>
-      <c r="S2" s="13"/>
-      <c r="T2" s="13"/>
-      <c r="U2" s="13"/>
-      <c r="V2" s="13"/>
-      <c r="W2" s="13"/>
-      <c r="X2" s="13"/>
-      <c r="Y2" s="13"/>
-      <c r="Z2" s="13"/>
-      <c r="AA2" s="13"/>
-      <c r="AB2" s="13"/>
-      <c r="AC2" s="13"/>
-      <c r="AD2" s="13"/>
-      <c r="AE2" s="13"/>
-      <c r="AF2" s="13"/>
-      <c r="AG2" s="13"/>
-    </row>
-    <row r="3" spans="1:33" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="22" t="s">
+      <c r="O2" s="10"/>
+      <c r="P2" s="12"/>
+      <c r="Q2" s="12"/>
+      <c r="R2" s="12"/>
+      <c r="S2" s="12"/>
+      <c r="T2" s="12"/>
+      <c r="U2" s="12"/>
+      <c r="V2" s="12"/>
+      <c r="W2" s="12"/>
+      <c r="X2" s="12"/>
+      <c r="Y2" s="12"/>
+      <c r="Z2" s="12"/>
+      <c r="AA2" s="12"/>
+      <c r="AB2" s="12"/>
+      <c r="AC2" s="12"/>
+      <c r="AD2" s="12"/>
+      <c r="AE2" s="12"/>
+      <c r="AF2" s="12"/>
+      <c r="AG2" s="12"/>
+    </row>
+    <row r="3" spans="1:33" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="22" t="s">
+      <c r="D3" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="22" t="s">
+      <c r="E3" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="16"/>
-      <c r="I3" s="16"/>
-      <c r="J3" s="16"/>
-      <c r="K3" s="16"/>
-      <c r="L3" s="16"/>
-      <c r="M3" s="16"/>
-      <c r="N3" s="16"/>
-      <c r="O3" s="16"/>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="5"/>
-      <c r="R3" s="5"/>
-      <c r="S3" s="5"/>
-      <c r="T3" s="5"/>
-      <c r="U3" s="5"/>
-      <c r="V3" s="5"/>
-      <c r="W3" s="5"/>
-    </row>
-    <row r="4" spans="1:33" s="4" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="23"/>
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="P4" s="6"/>
-      <c r="Q4" s="6"/>
-      <c r="R4" s="6"/>
-      <c r="S4" s="6"/>
-      <c r="T4" s="6"/>
-      <c r="U4" s="6"/>
-      <c r="V4" s="6"/>
-      <c r="W4" s="6"/>
-    </row>
-    <row r="5" spans="1:33" s="4" customFormat="1" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="24"/>
-      <c r="B5" s="24"/>
-      <c r="C5" s="24"/>
-      <c r="D5" s="24"/>
-      <c r="E5" s="24"/>
-      <c r="P5" s="6"/>
-      <c r="Q5" s="6"/>
-      <c r="R5" s="6"/>
-      <c r="S5" s="6"/>
-      <c r="T5" s="6"/>
-      <c r="U5" s="6"/>
-      <c r="V5" s="6"/>
-      <c r="W5" s="6"/>
-    </row>
-    <row r="6" spans="1:33" s="3" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A6" s="2"/>
-      <c r="B6" s="7" t="s">
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="15"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="15"/>
+      <c r="K3" s="15"/>
+      <c r="L3" s="15"/>
+      <c r="M3" s="15"/>
+      <c r="N3" s="15"/>
+      <c r="O3" s="15"/>
+      <c r="P3" s="4"/>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="4"/>
+      <c r="S3" s="4"/>
+      <c r="T3" s="4"/>
+      <c r="U3" s="4"/>
+      <c r="V3" s="4"/>
+      <c r="W3" s="4"/>
+    </row>
+    <row r="4" spans="1:33" s="3" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="26"/>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="P4" s="5"/>
+      <c r="Q4" s="5"/>
+      <c r="R4" s="5"/>
+      <c r="S4" s="5"/>
+      <c r="T4" s="5"/>
+      <c r="U4" s="5"/>
+      <c r="V4" s="5"/>
+      <c r="W4" s="5"/>
+    </row>
+    <row r="5" spans="1:33" s="3" customFormat="1" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="27"/>
+      <c r="B5" s="27"/>
+      <c r="C5" s="27"/>
+      <c r="D5" s="27"/>
+      <c r="E5" s="27"/>
+      <c r="P5" s="5"/>
+      <c r="Q5" s="5"/>
+      <c r="R5" s="5"/>
+      <c r="S5" s="5"/>
+      <c r="T5" s="5"/>
+      <c r="U5" s="5"/>
+      <c r="V5" s="5"/>
+      <c r="W5" s="5"/>
+    </row>
+    <row r="6" spans="1:33" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A6" s="15"/>
+      <c r="B6" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="7">
         <v>2101010011</v>
       </c>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15"/>
-      <c r="I6" s="15"/>
-      <c r="J6" s="15"/>
-      <c r="K6" s="15"/>
-      <c r="L6" s="15"/>
-      <c r="M6" s="15"/>
-      <c r="N6" s="15"/>
-      <c r="O6" s="15"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="5"/>
-      <c r="R6" s="5"/>
-      <c r="S6" s="5"/>
-      <c r="T6" s="5"/>
-      <c r="U6" s="5"/>
-      <c r="V6" s="5"/>
-      <c r="W6" s="5"/>
-    </row>
-    <row r="7" spans="1:33" s="3" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A7" s="2"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="15"/>
-      <c r="I7" s="15"/>
-      <c r="J7" s="15"/>
-      <c r="K7" s="15"/>
-      <c r="L7" s="15"/>
-      <c r="M7" s="15"/>
-      <c r="N7" s="15"/>
-      <c r="O7" s="15"/>
-      <c r="P7" s="5"/>
-      <c r="Q7" s="5"/>
-      <c r="R7" s="5"/>
-      <c r="S7" s="5"/>
-      <c r="T7" s="5"/>
-      <c r="U7" s="5"/>
-      <c r="V7" s="5"/>
-      <c r="W7" s="5"/>
-    </row>
-    <row r="8" spans="1:33" s="3" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="15"/>
-      <c r="J8" s="15"/>
-      <c r="K8" s="15"/>
-      <c r="L8" s="15"/>
-      <c r="M8" s="15"/>
-      <c r="N8" s="15"/>
-      <c r="O8" s="15"/>
-      <c r="P8" s="5"/>
-      <c r="Q8" s="5"/>
-      <c r="R8" s="5"/>
-      <c r="S8" s="5"/>
-      <c r="T8" s="5"/>
-      <c r="U8" s="5"/>
-      <c r="V8" s="5"/>
-      <c r="W8" s="5"/>
-    </row>
-    <row r="9" spans="1:33" s="3" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="15"/>
-      <c r="J9" s="15"/>
-      <c r="K9" s="15"/>
-      <c r="L9" s="15"/>
-      <c r="M9" s="15"/>
-      <c r="N9" s="15"/>
-      <c r="O9" s="15"/>
-      <c r="P9" s="5"/>
-      <c r="Q9" s="5"/>
-      <c r="R9" s="5"/>
-      <c r="S9" s="5"/>
-      <c r="T9" s="5"/>
-      <c r="U9" s="5"/>
-      <c r="V9" s="5"/>
-      <c r="W9" s="5"/>
-    </row>
-    <row r="10" spans="1:33" s="3" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="15"/>
-      <c r="I10" s="15"/>
-      <c r="J10" s="15"/>
-      <c r="K10" s="15"/>
-      <c r="L10" s="15"/>
-      <c r="M10" s="15"/>
-      <c r="N10" s="15"/>
-      <c r="O10" s="15"/>
-      <c r="P10" s="5"/>
-      <c r="Q10" s="5"/>
-      <c r="R10" s="5"/>
-      <c r="S10" s="5"/>
-      <c r="T10" s="5"/>
-      <c r="U10" s="5"/>
-      <c r="V10" s="5"/>
-      <c r="W10" s="5"/>
-    </row>
-    <row r="11" spans="1:33" s="3" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="15"/>
-      <c r="I11" s="15"/>
-      <c r="J11" s="15"/>
-      <c r="K11" s="15"/>
-      <c r="L11" s="15"/>
-      <c r="M11" s="15"/>
-      <c r="N11" s="15"/>
-      <c r="O11" s="15"/>
-      <c r="P11" s="5"/>
-      <c r="Q11" s="5"/>
-      <c r="R11" s="5"/>
-      <c r="S11" s="5"/>
-      <c r="T11" s="5"/>
-      <c r="U11" s="5"/>
-      <c r="V11" s="5"/>
-      <c r="W11" s="5"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="14"/>
+      <c r="N6" s="14"/>
+      <c r="O6" s="14"/>
+      <c r="P6" s="4"/>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="4"/>
+      <c r="S6" s="4"/>
+      <c r="T6" s="4"/>
+      <c r="U6" s="4"/>
+      <c r="V6" s="4"/>
+      <c r="W6" s="4"/>
+    </row>
+    <row r="7" spans="1:33" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A7" s="15"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="14"/>
+      <c r="J7" s="14"/>
+      <c r="K7" s="14"/>
+      <c r="L7" s="14"/>
+      <c r="M7" s="14"/>
+      <c r="N7" s="14"/>
+      <c r="O7" s="14"/>
+      <c r="P7" s="4"/>
+      <c r="Q7" s="4"/>
+      <c r="R7" s="4"/>
+      <c r="S7" s="4"/>
+      <c r="T7" s="4"/>
+      <c r="U7" s="4"/>
+      <c r="V7" s="4"/>
+      <c r="W7" s="4"/>
+    </row>
+    <row r="8" spans="1:33" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A8" s="15"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="14"/>
+      <c r="L8" s="14"/>
+      <c r="M8" s="14"/>
+      <c r="N8" s="14"/>
+      <c r="O8" s="14"/>
+      <c r="P8" s="4"/>
+      <c r="Q8" s="4"/>
+      <c r="R8" s="4"/>
+      <c r="S8" s="4"/>
+      <c r="T8" s="4"/>
+      <c r="U8" s="4"/>
+      <c r="V8" s="4"/>
+      <c r="W8" s="4"/>
+    </row>
+    <row r="9" spans="1:33" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A9" s="15"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="14"/>
+      <c r="H9" s="14"/>
+      <c r="I9" s="14"/>
+      <c r="J9" s="14"/>
+      <c r="K9" s="14"/>
+      <c r="L9" s="14"/>
+      <c r="M9" s="14"/>
+      <c r="N9" s="14"/>
+      <c r="O9" s="14"/>
+      <c r="P9" s="4"/>
+      <c r="Q9" s="4"/>
+      <c r="R9" s="4"/>
+      <c r="S9" s="4"/>
+      <c r="T9" s="4"/>
+      <c r="U9" s="4"/>
+      <c r="V9" s="4"/>
+      <c r="W9" s="4"/>
+    </row>
+    <row r="10" spans="1:33" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A10" s="15"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="14"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="14"/>
+      <c r="J10" s="14"/>
+      <c r="K10" s="14"/>
+      <c r="L10" s="14"/>
+      <c r="M10" s="14"/>
+      <c r="N10" s="14"/>
+      <c r="O10" s="14"/>
+      <c r="P10" s="4"/>
+      <c r="Q10" s="4"/>
+      <c r="R10" s="4"/>
+      <c r="S10" s="4"/>
+      <c r="T10" s="4"/>
+      <c r="U10" s="4"/>
+      <c r="V10" s="4"/>
+      <c r="W10" s="4"/>
+    </row>
+    <row r="11" spans="1:33" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A11" s="15"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
+      <c r="H11" s="14"/>
+      <c r="I11" s="14"/>
+      <c r="J11" s="14"/>
+      <c r="K11" s="14"/>
+      <c r="L11" s="14"/>
+      <c r="M11" s="14"/>
+      <c r="N11" s="14"/>
+      <c r="O11" s="14"/>
+      <c r="P11" s="4"/>
+      <c r="Q11" s="4"/>
+      <c r="R11" s="4"/>
+      <c r="S11" s="4"/>
+      <c r="T11" s="4"/>
+      <c r="U11" s="4"/>
+      <c r="V11" s="4"/>
+      <c r="W11" s="4"/>
     </row>
     <row r="12" spans="1:33" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25"/>
     <row r="13" spans="1:33" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="25"/>
-      <c r="B13" s="26" t="s">
+      <c r="A13" s="16"/>
+      <c r="B13" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="27"/>
-      <c r="D13" s="27"/>
-      <c r="E13" s="27"/>
-      <c r="F13" s="27"/>
-      <c r="G13" s="26" t="s">
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="H13" s="27"/>
-      <c r="I13" s="27"/>
-      <c r="J13" s="27"/>
-      <c r="K13" s="27"/>
-      <c r="P13" s="25"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="18"/>
+      <c r="J13" s="18"/>
+      <c r="K13" s="18"/>
+      <c r="P13" s="16"/>
     </row>
     <row r="14" spans="1:33" customFormat="1" ht="159" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="25"/>
-      <c r="B14" s="28"/>
-      <c r="C14" s="28"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="28"/>
-      <c r="F14" s="28"/>
-      <c r="G14" s="28"/>
-      <c r="H14" s="28"/>
-      <c r="I14" s="28"/>
-      <c r="J14" s="28"/>
-      <c r="K14" s="28"/>
-      <c r="P14" s="25"/>
+      <c r="A14" s="16"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="19"/>
+      <c r="K14" s="19"/>
+      <c r="P14" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="12">
